--- a/artfynd/A 54674-2023 artfynd.xlsx
+++ b/artfynd/A 54674-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,236 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125976143</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kampåkern, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>607658</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6908998</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125976196</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kampåkern, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607658</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6908998</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54674-2023 artfynd.xlsx
+++ b/artfynd/A 54674-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125853615</v>
       </c>
       <c r="B2" t="n">
-        <v>56958</v>
+        <v>56959</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>125976143</v>
       </c>
       <c r="B3" t="n">
-        <v>58084</v>
+        <v>58085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>125976196</v>
       </c>
       <c r="B4" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,6 +1018,121 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126128036</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Isbrickan, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>607687</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6908912</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Attmar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54674-2023 artfynd.xlsx
+++ b/artfynd/A 54674-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125853615</v>
       </c>
       <c r="B2" t="n">
-        <v>56959</v>
+        <v>56963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>125976143</v>
       </c>
       <c r="B3" t="n">
-        <v>58085</v>
+        <v>58089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>125976196</v>
       </c>
       <c r="B4" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>126128036</v>
       </c>
       <c r="B5" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 54674-2023 artfynd.xlsx
+++ b/artfynd/A 54674-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125853615</v>
       </c>
       <c r="B2" t="n">
-        <v>56963</v>
+        <v>56964</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>125976143</v>
       </c>
       <c r="B3" t="n">
-        <v>58089</v>
+        <v>58092</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>125976196</v>
       </c>
       <c r="B4" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>126128036</v>
       </c>
       <c r="B5" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
